--- a/react_web_tests/test_report.xlsx
+++ b/react_web_tests/test_report.xlsx
@@ -707,7 +707,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Generated: 2026-06-11 14:55:25   |   App URL: http://localhost:5173</t>
+          <t xml:space="preserve">  Generated: 2026-06-14 22:20:23   |   App URL: http://localhost:5173/CampusConnect_web/</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>871.4s</t>
+          <t>884.4s</t>
         </is>
       </c>
     </row>
@@ -1168,11 +1168,11 @@
         </is>
       </c>
       <c r="D4" s="23" t="n">
-        <v>3.196</v>
+        <v>3.089</v>
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:41:02</t>
+          <t>2026-06-14 22:05:47</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
@@ -1196,11 +1196,11 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>4.211</v>
+        <v>4.215</v>
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:41:06</t>
+          <t>2026-06-14 22:05:51</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
@@ -1224,11 +1224,11 @@
         </is>
       </c>
       <c r="D6" s="23" t="n">
-        <v>4.367</v>
+        <v>4.391</v>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:41:10</t>
+          <t>2026-06-14 22:05:56</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>4.363</v>
+        <v>4.667</v>
       </c>
       <c r="E7" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:41:15</t>
+          <t>2026-06-14 22:06:00</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
@@ -1280,11 +1280,11 @@
         </is>
       </c>
       <c r="D8" s="23" t="n">
-        <v>5.425</v>
+        <v>5.502</v>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:41:20</t>
+          <t>2026-06-14 22:06:06</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
@@ -1308,11 +1308,11 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>4.242</v>
+        <v>4.185</v>
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:41:24</t>
+          <t>2026-06-14 22:06:10</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -1336,11 +1336,11 @@
         </is>
       </c>
       <c r="D10" s="23" t="n">
-        <v>4.297</v>
+        <v>4.284</v>
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:41:29</t>
+          <t>2026-06-14 22:06:14</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
@@ -1364,11 +1364,11 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>6.402</v>
+        <v>6.379</v>
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:41:35</t>
+          <t>2026-06-14 22:06:21</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
@@ -1392,16 +1392,16 @@
         </is>
       </c>
       <c r="D12" s="23" t="n">
-        <v>6.875</v>
+        <v>6.412</v>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:41:42</t>
+          <t>2026-06-14 22:06:27</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>Login with correct credentials succeeded. Redirected to 'http://localhost:5173/'.</t>
+          <t>Login with correct credentials succeeded. Redirected to 'http://localhost:5173/CampusConnect_web/#/'.</t>
         </is>
       </c>
     </row>
@@ -1420,11 +1420,11 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>5.158</v>
+        <v>5.093</v>
       </c>
       <c r="E13" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:41:47</t>
+          <t>2026-06-14 22:06:32</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
@@ -1448,11 +1448,11 @@
         </is>
       </c>
       <c r="D14" s="23" t="n">
-        <v>5.132</v>
+        <v>5.082</v>
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:41:52</t>
+          <t>2026-06-14 22:06:37</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
@@ -1476,11 +1476,11 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.14</v>
+        <v>5.118</v>
       </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:41:57</t>
+          <t>2026-06-14 22:06:42</t>
         </is>
       </c>
       <c r="F15" s="28" t="inlineStr">
@@ -1504,11 +1504,11 @@
         </is>
       </c>
       <c r="D16" s="23" t="n">
-        <v>5.177</v>
+        <v>5.097</v>
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:42:03</t>
+          <t>2026-06-14 22:06:48</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>8.318</v>
+        <v>8.223000000000001</v>
       </c>
       <c r="E17" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:42:11</t>
+          <t>2026-06-14 22:06:56</t>
         </is>
       </c>
       <c r="F17" s="28" t="inlineStr">
@@ -1560,11 +1560,11 @@
         </is>
       </c>
       <c r="D18" s="23" t="n">
-        <v>6.436</v>
+        <v>6.361</v>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:42:17</t>
+          <t>2026-06-14 22:07:02</t>
         </is>
       </c>
       <c r="F18" s="24" t="inlineStr">
@@ -1588,11 +1588,11 @@
         </is>
       </c>
       <c r="D19" s="27" t="n">
-        <v>5.201</v>
+        <v>5.138</v>
       </c>
       <c r="E19" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:55:10</t>
+          <t>2026-06-14 22:19:56</t>
         </is>
       </c>
       <c r="F19" s="28" t="inlineStr">
@@ -1616,11 +1616,11 @@
         </is>
       </c>
       <c r="D20" s="23" t="n">
-        <v>3.12</v>
+        <v>6.069</v>
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:55:13</t>
+          <t>2026-06-14 22:20:02</t>
         </is>
       </c>
       <c r="F20" s="24" t="inlineStr">
@@ -1644,11 +1644,11 @@
         </is>
       </c>
       <c r="D21" s="27" t="n">
-        <v>3.116</v>
+        <v>6.063</v>
       </c>
       <c r="E21" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:55:16</t>
+          <t>2026-06-14 22:20:08</t>
         </is>
       </c>
       <c r="F21" s="28" t="inlineStr">
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="D22" s="23" t="n">
-        <v>3.115</v>
+        <v>6.07</v>
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:55:19</t>
+          <t>2026-06-14 22:20:14</t>
         </is>
       </c>
       <c r="F22" s="24" t="inlineStr">
@@ -1700,11 +1700,11 @@
         </is>
       </c>
       <c r="D23" s="27" t="n">
-        <v>3.118</v>
+        <v>6.06</v>
       </c>
       <c r="E23" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:55:22</t>
+          <t>2026-06-14 22:20:21</t>
         </is>
       </c>
       <c r="F23" s="28" t="inlineStr">
@@ -1822,11 +1822,11 @@
         </is>
       </c>
       <c r="D4" s="23" t="n">
-        <v>6.176</v>
+        <v>6.087</v>
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:42:23</t>
+          <t>2026-06-14 22:07:08</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
@@ -1850,11 +1850,11 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>6.232</v>
+        <v>6.122</v>
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:42:30</t>
+          <t>2026-06-14 22:07:14</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
@@ -1878,11 +1878,11 @@
         </is>
       </c>
       <c r="D6" s="23" t="n">
-        <v>6.134</v>
+        <v>6.088</v>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:42:36</t>
+          <t>2026-06-14 22:07:20</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -1906,11 +1906,11 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>9.231999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="E7" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:42:45</t>
+          <t>2026-06-14 22:07:30</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
@@ -1934,11 +1934,11 @@
         </is>
       </c>
       <c r="D8" s="23" t="n">
-        <v>11.352</v>
+        <v>11.329</v>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:42:56</t>
+          <t>2026-06-14 22:07:41</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
@@ -1962,11 +1962,11 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>11.272</v>
+        <v>11.2</v>
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:43:08</t>
+          <t>2026-06-14 22:07:52</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -1990,16 +1990,16 @@
         </is>
       </c>
       <c r="D10" s="23" t="n">
-        <v>6.18</v>
+        <v>6.085</v>
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:43:14</t>
+          <t>2026-06-14 22:07:58</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>Freelancer cards display names correctly. Found: API QA Engineer, Achyuth.</t>
+          <t>Freelancer cards display names correctly. Found: Achyuth.</t>
         </is>
       </c>
     </row>
@@ -2018,16 +2018,16 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>6.161</v>
+        <v>6.084</v>
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:43:20</t>
+          <t>2026-06-14 22:08:04</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>Freelancer cards correctly display academic departments (e.g. 'Computer Science').</t>
+          <t>Freelancer cards correctly display academic departments (e.g. 'Computer science').</t>
         </is>
       </c>
     </row>
@@ -2046,16 +2046,16 @@
         </is>
       </c>
       <c r="D12" s="23" t="n">
-        <v>6.133</v>
+        <v>6.066</v>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:43:26</t>
+          <t>2026-06-14 22:08:10</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>Freelancer cards display skill chips correctly (3 chips found across all cards).</t>
+          <t>Freelancer cards display skill chips correctly (1 chips found across all cards).</t>
         </is>
       </c>
     </row>
@@ -2074,11 +2074,11 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>6.151</v>
+        <v>6.082</v>
       </c>
       <c r="E13" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:43:32</t>
+          <t>2026-06-14 22:08:17</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="D14" s="23" t="n">
-        <v>9.189</v>
+        <v>9.137</v>
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:43:42</t>
+          <t>2026-06-14 22:08:26</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>Clicking freelancer card navigated to profile page at 'http://localhost:5173/profile/AUV1reaQquP85Ya7oJ7zWgK4vED2'.</t>
+          <t>Clicking freelancer card navigated to profile page at 'http://localhost:5173/CampusConnect_web/#/profile/vAaAiqCoNYdo0MUyzIQSBL2AYvS2'.</t>
         </is>
       </c>
     </row>
@@ -2130,11 +2130,11 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>9.275</v>
+        <v>9.175000000000001</v>
       </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:43:51</t>
+          <t>2026-06-14 22:08:35</t>
         </is>
       </c>
       <c r="F15" s="28" t="inlineStr">
@@ -2158,11 +2158,11 @@
         </is>
       </c>
       <c r="D16" s="23" t="n">
-        <v>9.196999999999999</v>
+        <v>9.132999999999999</v>
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:44:00</t>
+          <t>2026-06-14 22:08:44</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">
@@ -2186,11 +2186,11 @@
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>9.214</v>
+        <v>9.148999999999999</v>
       </c>
       <c r="E17" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:44:09</t>
+          <t>2026-06-14 22:08:53</t>
         </is>
       </c>
       <c r="F17" s="28" t="inlineStr">
@@ -2214,11 +2214,11 @@
         </is>
       </c>
       <c r="D18" s="23" t="n">
-        <v>11.19</v>
+        <v>11.152</v>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:44:20</t>
+          <t>2026-06-14 22:09:04</t>
         </is>
       </c>
       <c r="F18" s="24" t="inlineStr">
@@ -2331,11 +2331,11 @@
         </is>
       </c>
       <c r="D4" s="23" t="n">
-        <v>6.209</v>
+        <v>6.154</v>
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:44:27</t>
+          <t>2026-06-14 22:09:10</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
@@ -2359,11 +2359,11 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>6.189</v>
+        <v>6.138</v>
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:44:33</t>
+          <t>2026-06-14 22:09:17</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
@@ -2387,11 +2387,11 @@
         </is>
       </c>
       <c r="D6" s="23" t="n">
-        <v>6.204</v>
+        <v>6.145</v>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:44:39</t>
+          <t>2026-06-14 22:09:23</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -2415,11 +2415,11 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>20.163</v>
+        <v>20.512</v>
       </c>
       <c r="E7" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:44:59</t>
+          <t>2026-06-14 22:09:43</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
@@ -2443,11 +2443,11 @@
         </is>
       </c>
       <c r="D8" s="23" t="n">
-        <v>8.228999999999999</v>
+        <v>8.151999999999999</v>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:45:07</t>
+          <t>2026-06-14 22:09:51</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
@@ -2471,11 +2471,11 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>8.196</v>
+        <v>8.128</v>
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:45:16</t>
+          <t>2026-06-14 22:09:59</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="D10" s="23" t="n">
-        <v>6.186</v>
+        <v>6.08</v>
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:45:22</t>
+          <t>2026-06-14 22:10:06</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
@@ -2527,11 +2527,11 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>6.132</v>
+        <v>6.118</v>
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:45:28</t>
+          <t>2026-06-14 22:10:12</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
@@ -2555,11 +2555,11 @@
         </is>
       </c>
       <c r="D12" s="23" t="n">
-        <v>6.132</v>
+        <v>6.068</v>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:45:34</t>
+          <t>2026-06-14 22:10:18</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
@@ -2583,11 +2583,11 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>6.147</v>
+        <v>6.088</v>
       </c>
       <c r="E13" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:45:40</t>
+          <t>2026-06-14 22:10:24</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
@@ -2611,11 +2611,11 @@
         </is>
       </c>
       <c r="D14" s="23" t="n">
-        <v>6.173</v>
+        <v>6.115</v>
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:45:46</t>
+          <t>2026-06-14 22:10:30</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
@@ -2639,11 +2639,11 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>6.151</v>
+        <v>6.096</v>
       </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:45:53</t>
+          <t>2026-06-14 22:10:36</t>
         </is>
       </c>
       <c r="F15" s="28" t="inlineStr">
@@ -2667,11 +2667,11 @@
         </is>
       </c>
       <c r="D16" s="23" t="n">
-        <v>6.147</v>
+        <v>6.102</v>
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:45:59</t>
+          <t>2026-06-14 22:10:42</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">
@@ -2695,11 +2695,11 @@
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>8.231999999999999</v>
+        <v>8.154</v>
       </c>
       <c r="E17" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:46:07</t>
+          <t>2026-06-14 22:10:50</t>
         </is>
       </c>
       <c r="F17" s="28" t="inlineStr">
@@ -2723,11 +2723,11 @@
         </is>
       </c>
       <c r="D18" s="23" t="n">
-        <v>14.737</v>
+        <v>14.862</v>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:46:22</t>
+          <t>2026-06-14 22:11:05</t>
         </is>
       </c>
       <c r="F18" s="24" t="inlineStr">
@@ -2751,11 +2751,11 @@
         </is>
       </c>
       <c r="D19" s="27" t="n">
-        <v>6.326</v>
+        <v>6.218</v>
       </c>
       <c r="E19" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:46:28</t>
+          <t>2026-06-14 22:11:11</t>
         </is>
       </c>
       <c r="F19" s="28" t="inlineStr">
@@ -2779,16 +2779,16 @@
         </is>
       </c>
       <c r="D20" s="23" t="n">
-        <v>9.222</v>
+        <v>9.183</v>
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:46:37</t>
+          <t>2026-06-14 22:11:21</t>
         </is>
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>Clicking gig card navigated to detail page at 'http://localhost:5173/gigs/a6diJnso1NZYnERqDp75'.</t>
+          <t>Clicking gig card navigated to detail page at 'http://localhost:5173/CampusConnect_web/#/gigs/mChZqyYPKy9aI6GGBdFe'.</t>
         </is>
       </c>
     </row>
@@ -2807,11 +2807,11 @@
         </is>
       </c>
       <c r="D21" s="27" t="n">
-        <v>9.222</v>
+        <v>9.161</v>
       </c>
       <c r="E21" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:46:46</t>
+          <t>2026-06-14 22:11:30</t>
         </is>
       </c>
       <c r="F21" s="28" t="inlineStr">
@@ -2835,11 +2835,11 @@
         </is>
       </c>
       <c r="D22" s="23" t="n">
-        <v>8.151</v>
+        <v>8.106999999999999</v>
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:46:55</t>
+          <t>2026-06-14 22:11:38</t>
         </is>
       </c>
       <c r="F22" s="24" t="inlineStr">
@@ -2863,11 +2863,11 @@
         </is>
       </c>
       <c r="D23" s="27" t="n">
-        <v>9.16</v>
+        <v>9.124000000000001</v>
       </c>
       <c r="E23" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:47:04</t>
+          <t>2026-06-14 22:11:47</t>
         </is>
       </c>
       <c r="F23" s="28" t="inlineStr">
@@ -2985,11 +2985,11 @@
         </is>
       </c>
       <c r="D4" s="23" t="n">
-        <v>6.154</v>
+        <v>6.098</v>
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:47:10</t>
+          <t>2026-06-14 22:11:53</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
@@ -3013,11 +3013,11 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>6.153</v>
+        <v>6.083</v>
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:47:16</t>
+          <t>2026-06-14 22:11:59</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
@@ -3041,11 +3041,11 @@
         </is>
       </c>
       <c r="D6" s="23" t="n">
-        <v>6.148</v>
+        <v>6.085</v>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:47:22</t>
+          <t>2026-06-14 22:12:05</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -3069,11 +3069,11 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>8.346</v>
+        <v>8.196999999999999</v>
       </c>
       <c r="E7" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:47:31</t>
+          <t>2026-06-14 22:12:13</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
@@ -3097,11 +3097,11 @@
         </is>
       </c>
       <c r="D8" s="23" t="n">
-        <v>8.239000000000001</v>
+        <v>9.161</v>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:47:39</t>
+          <t>2026-06-14 22:12:23</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
@@ -3125,11 +3125,11 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>10.268</v>
+        <v>11.19</v>
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:47:49</t>
+          <t>2026-06-14 22:12:34</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -3153,11 +3153,11 @@
         </is>
       </c>
       <c r="D10" s="23" t="n">
-        <v>10.32</v>
+        <v>11.278</v>
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:47:59</t>
+          <t>2026-06-14 22:12:45</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
@@ -3181,16 +3181,16 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>15.57</v>
+        <v>16.582</v>
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:48:15</t>
+          <t>2026-06-14 22:13:02</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>Team 'E2E Squad 3525' created successfully with 'React' skill via the Create Team form.</t>
+          <t>Team 'E2E Squad 3CBD' created successfully with 'React' skill via the Create Team form.</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3209,16 @@
         </is>
       </c>
       <c r="D12" s="23" t="n">
-        <v>6.185</v>
+        <v>6.177</v>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:48:21</t>
+          <t>2026-06-14 22:13:08</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>Teams listing shows created teams (6 team cards found).</t>
+          <t>Teams listing shows created teams (7 team cards found).</t>
         </is>
       </c>
     </row>
@@ -3237,11 +3237,11 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>6.267</v>
+        <v>6.251</v>
       </c>
       <c r="E13" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:48:27</t>
+          <t>2026-06-14 22:13:14</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
@@ -3265,11 +3265,11 @@
         </is>
       </c>
       <c r="D14" s="23" t="n">
-        <v>6.137</v>
+        <v>6.115</v>
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:48:33</t>
+          <t>2026-06-14 22:13:20</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
@@ -3293,11 +3293,11 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>8.196999999999999</v>
+        <v>8.159000000000001</v>
       </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:48:42</t>
+          <t>2026-06-14 22:13:28</t>
         </is>
       </c>
       <c r="F15" s="28" t="inlineStr">
@@ -3321,11 +3321,11 @@
         </is>
       </c>
       <c r="D16" s="23" t="n">
-        <v>8.198</v>
+        <v>8.138</v>
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:48:50</t>
+          <t>2026-06-14 22:13:36</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">
@@ -3349,11 +3349,11 @@
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>8.231</v>
+        <v>8.144</v>
       </c>
       <c r="E17" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:48:58</t>
+          <t>2026-06-14 22:13:45</t>
         </is>
       </c>
       <c r="F17" s="28" t="inlineStr">
@@ -3377,11 +3377,11 @@
         </is>
       </c>
       <c r="D18" s="23" t="n">
-        <v>8.27</v>
+        <v>8.119</v>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:49:06</t>
+          <t>2026-06-14 22:13:53</t>
         </is>
       </c>
       <c r="F18" s="24" t="inlineStr">
@@ -3494,11 +3494,11 @@
         </is>
       </c>
       <c r="D4" s="23" t="n">
-        <v>6.129</v>
+        <v>6.108</v>
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:50:30</t>
+          <t>2026-06-14 22:15:16</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
@@ -3522,11 +3522,11 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>6.16</v>
+        <v>6.074</v>
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:50:36</t>
+          <t>2026-06-14 22:15:22</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
@@ -3550,11 +3550,11 @@
         </is>
       </c>
       <c r="D6" s="23" t="n">
-        <v>8.109999999999999</v>
+        <v>8.025</v>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:50:44</t>
+          <t>2026-06-14 22:15:30</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -3578,11 +3578,11 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>8.096</v>
+        <v>8.032</v>
       </c>
       <c r="E7" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:50:52</t>
+          <t>2026-06-14 22:15:38</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
@@ -3606,11 +3606,11 @@
         </is>
       </c>
       <c r="D8" s="23" t="n">
-        <v>6.144</v>
+        <v>6.094</v>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:50:59</t>
+          <t>2026-06-14 22:15:44</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
@@ -3634,11 +3634,11 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>8.093</v>
+        <v>8.041</v>
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:51:07</t>
+          <t>2026-06-14 22:15:52</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -3662,11 +3662,11 @@
         </is>
       </c>
       <c r="D10" s="23" t="n">
-        <v>8.090999999999999</v>
+        <v>8.039</v>
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:51:15</t>
+          <t>2026-06-14 22:16:00</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
@@ -3690,11 +3690,11 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>8.112</v>
+        <v>8.044</v>
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:51:23</t>
+          <t>2026-06-14 22:16:08</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
@@ -3718,11 +3718,11 @@
         </is>
       </c>
       <c r="D12" s="23" t="n">
-        <v>10.115</v>
+        <v>10.033</v>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:51:33</t>
+          <t>2026-06-14 22:16:18</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
@@ -3746,11 +3746,11 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>10.223</v>
+        <v>10.134</v>
       </c>
       <c r="E13" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:51:43</t>
+          <t>2026-06-14 22:16:28</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
@@ -3774,11 +3774,11 @@
         </is>
       </c>
       <c r="D14" s="23" t="n">
-        <v>8.109</v>
+        <v>8.032999999999999</v>
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:51:51</t>
+          <t>2026-06-14 22:16:36</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
@@ -3802,11 +3802,11 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>17.285</v>
+        <v>17.148</v>
       </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:52:09</t>
+          <t>2026-06-14 22:16:53</t>
         </is>
       </c>
       <c r="F15" s="28" t="inlineStr">
@@ -3830,11 +3830,11 @@
         </is>
       </c>
       <c r="D16" s="23" t="n">
-        <v>12.264</v>
+        <v>12.22</v>
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:52:21</t>
+          <t>2026-06-14 22:17:06</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">
@@ -3945,11 +3945,11 @@
         </is>
       </c>
       <c r="D4" s="23" t="n">
-        <v>7.245</v>
+        <v>7.216</v>
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:49:14</t>
+          <t>2026-06-14 22:14:00</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
@@ -3973,11 +3973,11 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>7.239</v>
+        <v>7.18</v>
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:49:21</t>
+          <t>2026-06-14 22:14:07</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
@@ -4001,11 +4001,11 @@
         </is>
       </c>
       <c r="D6" s="23" t="n">
-        <v>7.264</v>
+        <v>7.197</v>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:49:28</t>
+          <t>2026-06-14 22:14:14</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -4029,11 +4029,11 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>7.271</v>
+        <v>7.201</v>
       </c>
       <c r="E7" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:49:35</t>
+          <t>2026-06-14 22:14:22</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
@@ -4057,11 +4057,11 @@
         </is>
       </c>
       <c r="D8" s="23" t="n">
-        <v>7.257</v>
+        <v>7.181</v>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:49:43</t>
+          <t>2026-06-14 22:14:29</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
@@ -4085,11 +4085,11 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>7.236</v>
+        <v>7.184</v>
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:49:50</t>
+          <t>2026-06-14 22:14:36</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -4113,11 +4113,11 @@
         </is>
       </c>
       <c r="D10" s="23" t="n">
-        <v>7.264</v>
+        <v>7.198</v>
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:49:57</t>
+          <t>2026-06-14 22:14:43</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
@@ -4141,11 +4141,11 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>7.27</v>
+        <v>7.19</v>
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:50:04</t>
+          <t>2026-06-14 22:14:50</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
@@ -4169,11 +4169,11 @@
         </is>
       </c>
       <c r="D12" s="23" t="n">
-        <v>19.465</v>
+        <v>19.293</v>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:50:24</t>
+          <t>2026-06-14 22:15:10</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
@@ -4280,11 +4280,11 @@
         </is>
       </c>
       <c r="D4" s="23" t="n">
-        <v>6.164</v>
+        <v>6.102</v>
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:52:27</t>
+          <t>2026-06-14 22:17:12</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
@@ -4308,11 +4308,11 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>6.163</v>
+        <v>6.118</v>
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:52:33</t>
+          <t>2026-06-14 22:17:18</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
@@ -4336,11 +4336,11 @@
         </is>
       </c>
       <c r="D6" s="23" t="n">
-        <v>6.144</v>
+        <v>6.099</v>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:52:39</t>
+          <t>2026-06-14 22:17:24</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -4364,11 +4364,11 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>6.132</v>
+        <v>6.099</v>
       </c>
       <c r="E7" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:52:45</t>
+          <t>2026-06-14 22:17:30</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
@@ -4392,11 +4392,11 @@
         </is>
       </c>
       <c r="D8" s="23" t="n">
-        <v>6.148</v>
+        <v>6.116</v>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:52:52</t>
+          <t>2026-06-14 22:17:36</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
@@ -4420,11 +4420,11 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>6.154</v>
+        <v>6.103</v>
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:52:58</t>
+          <t>2026-06-14 22:17:42</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -4448,11 +4448,11 @@
         </is>
       </c>
       <c r="D10" s="23" t="n">
-        <v>8.220000000000001</v>
+        <v>8.151999999999999</v>
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:53:06</t>
+          <t>2026-06-14 22:17:50</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
@@ -4476,11 +4476,11 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>6.156</v>
+        <v>6.089</v>
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:53:12</t>
+          <t>2026-06-14 22:17:56</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
@@ -4504,11 +4504,11 @@
         </is>
       </c>
       <c r="D12" s="23" t="n">
-        <v>8.167</v>
+        <v>8.119</v>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:53:20</t>
+          <t>2026-06-14 22:18:05</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
@@ -4532,11 +4532,11 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>9.199</v>
+        <v>9.132999999999999</v>
       </c>
       <c r="E13" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:53:29</t>
+          <t>2026-06-14 22:18:14</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="D14" s="23" t="n">
-        <v>11.289</v>
+        <v>11.195</v>
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:53:41</t>
+          <t>2026-06-14 22:18:25</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
@@ -4588,11 +4588,11 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>5.137</v>
+        <v>5.09</v>
       </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:53:46</t>
+          <t>2026-06-14 22:18:30</t>
         </is>
       </c>
       <c r="F15" s="28" t="inlineStr">
@@ -4616,11 +4616,11 @@
         </is>
       </c>
       <c r="D16" s="23" t="n">
-        <v>9.193</v>
+        <v>9.129</v>
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:53:55</t>
+          <t>2026-06-14 22:18:39</t>
         </is>
       </c>
       <c r="F16" s="24" t="inlineStr">
@@ -4731,11 +4731,11 @@
         </is>
       </c>
       <c r="D4" s="23" t="n">
-        <v>6.197</v>
+        <v>6.106</v>
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:54:01</t>
+          <t>2026-06-14 22:18:45</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
@@ -4759,11 +4759,11 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>6.161</v>
+        <v>6.083</v>
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:54:07</t>
+          <t>2026-06-14 22:18:51</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
@@ -4787,11 +4787,11 @@
         </is>
       </c>
       <c r="D6" s="23" t="n">
-        <v>6.144</v>
+        <v>6.097</v>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:54:14</t>
+          <t>2026-06-14 22:18:57</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -4815,11 +4815,11 @@
         </is>
       </c>
       <c r="D7" s="27" t="n">
-        <v>6.149</v>
+        <v>6.097</v>
       </c>
       <c r="E7" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:54:20</t>
+          <t>2026-06-14 22:19:04</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
@@ -4843,11 +4843,11 @@
         </is>
       </c>
       <c r="D8" s="23" t="n">
-        <v>6.144</v>
+        <v>6.089</v>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:54:26</t>
+          <t>2026-06-14 22:19:10</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
@@ -4871,11 +4871,11 @@
         </is>
       </c>
       <c r="D9" s="27" t="n">
-        <v>6.161</v>
+        <v>6.089</v>
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:54:32</t>
+          <t>2026-06-14 22:19:16</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -4899,11 +4899,11 @@
         </is>
       </c>
       <c r="D10" s="23" t="n">
-        <v>6.18</v>
+        <v>6.092</v>
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:54:38</t>
+          <t>2026-06-14 22:19:22</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
@@ -4927,11 +4927,11 @@
         </is>
       </c>
       <c r="D11" s="27" t="n">
-        <v>6.123</v>
+        <v>6.084</v>
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:54:44</t>
+          <t>2026-06-14 22:19:28</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
@@ -4955,11 +4955,11 @@
         </is>
       </c>
       <c r="D12" s="23" t="n">
-        <v>3.155</v>
+        <v>6.109</v>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>2026-06-11 14:54:48</t>
+          <t>2026-06-14 22:19:34</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
@@ -4983,16 +4983,16 @@
         </is>
       </c>
       <c r="D13" s="27" t="n">
-        <v>17.305</v>
+        <v>17.139</v>
       </c>
       <c r="E13" s="26" t="inlineStr">
         <is>
-          <t>2026-06-11 14:55:05</t>
+          <t>2026-06-14 22:19:51</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>Browser back button correctly navigated to the previous page: 'http://localhost:5173/gigs'.</t>
+          <t>Browser back button correctly navigated to the previous page: 'http://localhost:5173/CampusConnect_web/#/gigs'.</t>
         </is>
       </c>
     </row>

--- a/react_web_tests/test_report.xlsx
+++ b/react_web_tests/test_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\achyu\Desktop\Projects\CampusConnect\web_platform\react_web_tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC300680-2AF6-4ED2-80CB-4FC9A0089CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE0817A-F5CD-4D17-B421-08394E35E955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="735">
   <si>
     <t xml:space="preserve">  CampusConnect React Web Platform — Selenium E2E Test Report</t>
   </si>
@@ -54,15 +54,6 @@
   </si>
   <si>
     <t>225</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>99.6%</t>
   </si>
   <si>
     <t>1928.1s</t>
@@ -2458,7 +2449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2520,6 +2511,18 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2530,32 +2533,23 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2881,32 +2875,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
     </row>
     <row r="3" spans="1:10" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2930,42 +2924,42 @@
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="3">
+        <v>225</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="35">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:10" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
+      <c r="A8" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
     </row>
     <row r="9" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>3</v>
@@ -2974,18 +2968,18 @@
         <v>4</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C10" s="7">
         <v>30</v>
@@ -2997,18 +2991,18 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C11" s="10">
         <v>25</v>
@@ -3020,18 +3014,18 @@
         <v>0</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C12" s="7">
         <v>35</v>
@@ -3043,18 +3037,18 @@
         <v>0</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C13" s="10">
         <v>25</v>
@@ -3066,18 +3060,18 @@
         <v>0</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C14" s="7">
         <v>25</v>
@@ -3089,18 +3083,18 @@
         <v>0</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="32" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C15" s="10">
         <v>15</v>
@@ -3111,19 +3105,19 @@
       <c r="E15" s="10">
         <v>0</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="24">
         <v>1</v>
       </c>
-      <c r="G15" s="33" t="s">
-        <v>20</v>
+      <c r="G15" s="23" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C16" s="7">
         <v>25</v>
@@ -3135,18 +3129,18 @@
         <v>0</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C17" s="10">
         <v>15</v>
@@ -3158,18 +3152,18 @@
         <v>0</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C18" s="7">
         <v>20</v>
@@ -3181,18 +3175,18 @@
         <v>0</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C19" s="10">
         <v>10</v>
@@ -3204,16 +3198,16 @@
         <v>0</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C20" s="6">
         <v>225</v>
@@ -3225,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G20" s="6"/>
     </row>
@@ -3254,469 +3248,476 @@
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
-        <v>644</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+        <v>641</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
-        <v>645</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="A2" s="32" t="s">
+        <v>642</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="F3" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="28"/>
+      <c r="G3" s="34"/>
     </row>
     <row r="4" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
         <v>1</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D4" s="17">
         <v>18.047000000000001</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>647</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>648</v>
-      </c>
-      <c r="G4" s="22"/>
+        <v>644</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>645</v>
+      </c>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>2</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" s="20">
         <v>11.597</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>650</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>651</v>
-      </c>
-      <c r="G5" s="22"/>
+        <v>647</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>648</v>
+      </c>
+      <c r="G5" s="26"/>
     </row>
     <row r="6" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>3</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D6" s="17">
         <v>11.516999999999999</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>653</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>654</v>
-      </c>
-      <c r="G6" s="22"/>
+        <v>650</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>651</v>
+      </c>
+      <c r="G6" s="26"/>
     </row>
     <row r="7" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18">
         <v>4</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D7" s="20">
         <v>18.074999999999999</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>656</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>657</v>
-      </c>
-      <c r="G7" s="22"/>
+        <v>653</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>654</v>
+      </c>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>5</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="17">
         <v>18.07</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>659</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>660</v>
-      </c>
-      <c r="G8" s="22"/>
+        <v>656</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>657</v>
+      </c>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D9" s="20">
         <v>18.044</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>662</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>663</v>
-      </c>
-      <c r="G9" s="22"/>
+        <v>659</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>660</v>
+      </c>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>7</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" s="17">
         <v>13.538</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>665</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>666</v>
-      </c>
-      <c r="G10" s="22"/>
+        <v>662</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>663</v>
+      </c>
+      <c r="G10" s="26"/>
     </row>
     <row r="11" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18">
         <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D11" s="20">
         <v>13.558</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>668</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>669</v>
-      </c>
-      <c r="G11" s="22"/>
+        <v>665</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>666</v>
+      </c>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>9</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D12" s="17">
         <v>13.472</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>671</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>672</v>
-      </c>
-      <c r="G12" s="22"/>
+        <v>668</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>669</v>
+      </c>
+      <c r="G12" s="26"/>
     </row>
     <row r="13" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
         <v>10</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13" s="20">
         <v>20.63</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>674</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>675</v>
-      </c>
-      <c r="G13" s="22"/>
+        <v>671</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>672</v>
+      </c>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
         <v>11</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D14" s="17">
         <v>6.55</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>677</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>678</v>
-      </c>
-      <c r="G14" s="22"/>
+        <v>674</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>675</v>
+      </c>
+      <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18">
         <v>12</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D15" s="20">
         <v>11.423999999999999</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>680</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>681</v>
-      </c>
-      <c r="G15" s="22"/>
+        <v>677</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>678</v>
+      </c>
+      <c r="G15" s="26"/>
     </row>
     <row r="16" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
         <v>13</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D16" s="17">
         <v>7.7489999999999997</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>683</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>684</v>
-      </c>
-      <c r="G16" s="22"/>
+        <v>680</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>681</v>
+      </c>
+      <c r="G16" s="26"/>
     </row>
     <row r="17" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18">
         <v>14</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D17" s="20">
         <v>13.489000000000001</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>686</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>687</v>
-      </c>
-      <c r="G17" s="22"/>
+        <v>683</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>684</v>
+      </c>
+      <c r="G17" s="26"/>
     </row>
     <row r="18" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
         <v>15</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D18" s="17">
         <v>11.358000000000001</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>689</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>690</v>
-      </c>
-      <c r="G18" s="22"/>
+        <v>686</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>687</v>
+      </c>
+      <c r="G18" s="26"/>
     </row>
     <row r="19" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18">
         <v>16</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D19" s="20">
         <v>13.359</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>692</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>693</v>
-      </c>
-      <c r="G19" s="22"/>
+        <v>689</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>690</v>
+      </c>
+      <c r="G19" s="26"/>
     </row>
     <row r="20" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
         <v>17</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D20" s="17">
         <v>11.407</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>695</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>696</v>
-      </c>
-      <c r="G20" s="22"/>
+        <v>692</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>693</v>
+      </c>
+      <c r="G20" s="26"/>
     </row>
     <row r="21" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18">
         <v>18</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D21" s="20">
         <v>11.375999999999999</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>698</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>699</v>
-      </c>
-      <c r="G21" s="22"/>
+        <v>695</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>696</v>
+      </c>
+      <c r="G21" s="26"/>
     </row>
     <row r="22" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <v>19</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D22" s="17">
         <v>11.343999999999999</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>701</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>702</v>
-      </c>
-      <c r="G22" s="22"/>
+        <v>698</v>
+      </c>
+      <c r="F22" s="31" t="s">
+        <v>699</v>
+      </c>
+      <c r="G22" s="26"/>
     </row>
     <row r="23" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18">
         <v>20</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D23" s="20">
         <v>7.758</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>704</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>705</v>
-      </c>
-      <c r="G23" s="22"/>
+        <v>701</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>702</v>
+      </c>
+      <c r="G23" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F22:G22"/>
@@ -3733,13 +3734,6 @@
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3760,259 +3754,264 @@
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
-        <v>706</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+        <v>703</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
-        <v>707</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="A2" s="32" t="s">
+        <v>704</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="F3" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="28"/>
+      <c r="G3" s="34"/>
     </row>
     <row r="4" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
         <v>1</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D4" s="17">
         <v>9.3879999999999999</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>709</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>710</v>
-      </c>
-      <c r="G4" s="22"/>
+        <v>706</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>707</v>
+      </c>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>2</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" s="20">
         <v>11.372</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>712</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>713</v>
-      </c>
-      <c r="G5" s="22"/>
+        <v>709</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>710</v>
+      </c>
+      <c r="G5" s="26"/>
     </row>
     <row r="6" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>3</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D6" s="17">
         <v>9.3840000000000003</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>715</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>716</v>
-      </c>
-      <c r="G6" s="22"/>
+        <v>712</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>713</v>
+      </c>
+      <c r="G6" s="26"/>
     </row>
     <row r="7" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18">
         <v>4</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D7" s="20">
         <v>9.4320000000000004</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>718</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>719</v>
-      </c>
-      <c r="G7" s="22"/>
+        <v>715</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>716</v>
+      </c>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>5</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="17">
         <v>9.4529999999999994</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>721</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>722</v>
-      </c>
-      <c r="G8" s="22"/>
+        <v>718</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>719</v>
+      </c>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D9" s="20">
         <v>11.457000000000001</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>724</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>725</v>
-      </c>
-      <c r="G9" s="22"/>
+        <v>721</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>722</v>
+      </c>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>7</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" s="17">
         <v>13.504</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>727</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>728</v>
-      </c>
-      <c r="G10" s="22"/>
+        <v>724</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>725</v>
+      </c>
+      <c r="G10" s="26"/>
     </row>
     <row r="11" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18">
         <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D11" s="20">
         <v>12.676</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>730</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>731</v>
-      </c>
-      <c r="G11" s="22"/>
+        <v>727</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>728</v>
+      </c>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>9</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D12" s="17">
         <v>15.5</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>733</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>734</v>
-      </c>
-      <c r="G12" s="22"/>
+        <v>730</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>731</v>
+      </c>
+      <c r="G12" s="26"/>
     </row>
     <row r="13" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
         <v>10</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13" s="20">
         <v>11.327</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>736</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>737</v>
-      </c>
-      <c r="G13" s="22"/>
+        <v>733</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>734</v>
+      </c>
+      <c r="G13" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="F6:G6"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="F7:G7"/>
@@ -4021,11 +4020,6 @@
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="F12:G12"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F6:G6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4046,679 +4040,696 @@
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+        <v>37</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="A2" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="F3" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="28"/>
+      <c r="G3" s="34"/>
     </row>
     <row r="4" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
         <v>1</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D4" s="17">
         <v>3.145</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="22"/>
+        <v>46</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>2</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" s="20">
         <v>4.1820000000000004</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="22"/>
+        <v>49</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="26"/>
     </row>
     <row r="6" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>3</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D6" s="17">
         <v>4.2679999999999998</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="22"/>
+        <v>52</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="26"/>
     </row>
     <row r="7" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18">
         <v>4</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D7" s="20">
         <v>4.3490000000000002</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="22"/>
+        <v>55</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>5</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="17">
         <v>5.4119999999999999</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="22"/>
+        <v>58</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D9" s="20">
         <v>4.218</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="22"/>
+        <v>61</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>7</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" s="17">
         <v>4.2939999999999996</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="22"/>
+        <v>64</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="26"/>
     </row>
     <row r="11" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18">
         <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D11" s="20">
         <v>6.4640000000000004</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="22"/>
+        <v>67</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>9</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D12" s="17">
         <v>6.3920000000000003</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" s="22"/>
+        <v>70</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="26"/>
     </row>
     <row r="13" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
         <v>10</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13" s="20">
         <v>5.1130000000000004</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="22"/>
+        <v>73</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
         <v>11</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D14" s="17">
         <v>5.1879999999999997</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="G14" s="22"/>
+        <v>76</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18">
         <v>12</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D15" s="20">
         <v>5.4009999999999998</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="G15" s="22"/>
+        <v>79</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="26"/>
     </row>
     <row r="16" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
         <v>13</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D16" s="17">
         <v>5.2560000000000002</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="G16" s="22"/>
+        <v>82</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="26"/>
     </row>
     <row r="17" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18">
         <v>14</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D17" s="20">
         <v>8.5969999999999995</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="G17" s="22"/>
+        <v>85</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="26"/>
     </row>
     <row r="18" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
         <v>15</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D18" s="17">
         <v>6.6070000000000002</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="G18" s="22"/>
+        <v>88</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" s="26"/>
     </row>
     <row r="19" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18">
         <v>16</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D19" s="20">
         <v>5.399</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G19" s="22"/>
+        <v>91</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19" s="26"/>
     </row>
     <row r="20" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
         <v>17</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D20" s="17">
         <v>5.4409999999999998</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="G20" s="22"/>
+        <v>94</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="G20" s="26"/>
     </row>
     <row r="21" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18">
         <v>18</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D21" s="20">
         <v>5.5330000000000004</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="G21" s="22"/>
+        <v>97</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" s="26"/>
     </row>
     <row r="22" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <v>19</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D22" s="17">
         <v>3.1829999999999998</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="G22" s="22"/>
+        <v>100</v>
+      </c>
+      <c r="F22" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" s="26"/>
     </row>
     <row r="23" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18">
         <v>20</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D23" s="20">
         <v>6.4909999999999997</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="G23" s="22"/>
+        <v>103</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="G23" s="26"/>
     </row>
     <row r="24" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
         <v>21</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D24" s="17">
         <v>5.0999999999999996</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="G24" s="22"/>
+        <v>106</v>
+      </c>
+      <c r="F24" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="G24" s="26"/>
     </row>
     <row r="25" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
         <v>22</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D25" s="20">
         <v>5.4459999999999997</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="G25" s="22"/>
+        <v>109</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" s="26"/>
     </row>
     <row r="26" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
         <v>23</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D26" s="17">
         <v>5.4720000000000004</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="G26" s="22"/>
+        <v>112</v>
+      </c>
+      <c r="F26" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="G26" s="26"/>
     </row>
     <row r="27" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18">
         <v>24</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D27" s="20">
         <v>8.4350000000000005</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="G27" s="22"/>
+        <v>115</v>
+      </c>
+      <c r="F27" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" s="26"/>
     </row>
     <row r="28" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
         <v>25</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D28" s="17">
         <v>7.2709999999999999</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="G28" s="22"/>
+        <v>118</v>
+      </c>
+      <c r="F28" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="G28" s="26"/>
     </row>
     <row r="29" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="18">
         <v>26</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D29" s="20">
         <v>5.3810000000000002</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="F29" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="G29" s="22"/>
+        <v>121</v>
+      </c>
+      <c r="F29" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="G29" s="26"/>
     </row>
     <row r="30" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14">
         <v>27</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D30" s="17">
         <v>6.2069999999999999</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="F30" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="G30" s="22"/>
+        <v>124</v>
+      </c>
+      <c r="F30" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="G30" s="26"/>
     </row>
     <row r="31" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="18">
         <v>28</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D31" s="20">
         <v>6.1849999999999996</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="F31" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="G31" s="22"/>
+        <v>127</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="G31" s="26"/>
     </row>
     <row r="32" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14">
         <v>29</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D32" s="17">
         <v>6.1779999999999999</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="F32" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="G32" s="22"/>
+        <v>130</v>
+      </c>
+      <c r="F32" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="G32" s="26"/>
     </row>
     <row r="33" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="18">
         <v>30</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D33" s="20">
         <v>6.18</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="F33" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="G33" s="22"/>
+        <v>133</v>
+      </c>
+      <c r="F33" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="G33" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F16:G16"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F31:G31"/>
@@ -4729,29 +4740,12 @@
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F8:G8"/>
     <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F18:G18"/>
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F16:G16"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4772,583 +4766,574 @@
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+        <v>135</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="A2" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="F3" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="28"/>
+      <c r="G3" s="34"/>
     </row>
     <row r="4" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
         <v>1</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D4" s="17">
         <v>14.603</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="G4" s="22"/>
+        <v>138</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>2</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" s="20">
         <v>6.1890000000000001</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="G5" s="22"/>
+        <v>141</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="G5" s="26"/>
     </row>
     <row r="6" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>3</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D6" s="17">
         <v>6.1369999999999996</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="G6" s="22"/>
+        <v>144</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="G6" s="26"/>
     </row>
     <row r="7" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18">
         <v>4</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D7" s="20">
         <v>9.4220000000000006</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="G7" s="22"/>
+        <v>147</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>5</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="17">
         <v>11.487</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="G8" s="22"/>
+        <v>150</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D9" s="20">
         <v>11.265000000000001</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="G9" s="22"/>
+        <v>153</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>7</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" s="17">
         <v>6.1580000000000004</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="G10" s="22"/>
+        <v>156</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="26"/>
     </row>
     <row r="11" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18">
         <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D11" s="20">
         <v>6.1420000000000003</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>163</v>
-      </c>
-      <c r="G11" s="22"/>
+        <v>159</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>9</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D12" s="17">
         <v>6.0970000000000004</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="G12" s="22"/>
+        <v>162</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="G12" s="26"/>
     </row>
     <row r="13" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
         <v>10</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13" s="20">
         <v>6.14</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="G13" s="22"/>
+        <v>165</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
         <v>11</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D14" s="17">
         <v>9.2319999999999993</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="G14" s="22"/>
+        <v>168</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18">
         <v>12</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D15" s="20">
         <v>9.2309999999999999</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="G15" s="22"/>
+        <v>171</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="G15" s="26"/>
     </row>
     <row r="16" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
         <v>13</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D16" s="17">
         <v>9.2449999999999992</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="G16" s="22"/>
+        <v>174</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="G16" s="26"/>
     </row>
     <row r="17" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18">
         <v>14</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D17" s="20">
         <v>9.23</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="G17" s="22"/>
+        <v>177</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="G17" s="26"/>
     </row>
     <row r="18" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
         <v>15</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D18" s="17">
         <v>11.206</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="G18" s="22"/>
+        <v>180</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="G18" s="26"/>
     </row>
     <row r="19" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18">
         <v>16</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D19" s="20">
         <v>6.12</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="G19" s="22"/>
+        <v>183</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="G19" s="26"/>
     </row>
     <row r="20" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
         <v>17</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D20" s="17">
         <v>8.2469999999999999</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="G20" s="22"/>
+        <v>186</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>187</v>
+      </c>
+      <c r="G20" s="26"/>
     </row>
     <row r="21" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18">
         <v>18</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D21" s="20">
         <v>19.350000000000001</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="G21" s="22"/>
+        <v>189</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="G21" s="26"/>
     </row>
     <row r="22" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <v>19</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D22" s="17">
         <v>11.364000000000001</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="G22" s="22"/>
+        <v>192</v>
+      </c>
+      <c r="F22" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="G22" s="26"/>
     </row>
     <row r="23" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18">
         <v>20</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D23" s="20">
         <v>8.1509999999999998</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="G23" s="22"/>
+        <v>195</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="G23" s="26"/>
     </row>
     <row r="24" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
         <v>21</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D24" s="17">
         <v>8.1579999999999995</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="G24" s="22"/>
+        <v>198</v>
+      </c>
+      <c r="F24" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="G24" s="26"/>
     </row>
     <row r="25" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
         <v>22</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D25" s="20">
         <v>6.1559999999999997</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="G25" s="22"/>
+        <v>201</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="G25" s="26"/>
     </row>
     <row r="26" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
         <v>23</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D26" s="17">
         <v>6.1180000000000003</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="G26" s="22"/>
+        <v>204</v>
+      </c>
+      <c r="F26" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="G26" s="26"/>
     </row>
     <row r="27" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18">
         <v>24</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D27" s="20">
         <v>9.24</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="G27" s="22"/>
+        <v>207</v>
+      </c>
+      <c r="F27" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="G27" s="26"/>
     </row>
     <row r="28" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
         <v>25</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D28" s="17">
         <v>8.1590000000000007</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="G28" s="22"/>
+        <v>210</v>
+      </c>
+      <c r="F28" s="31" t="s">
+        <v>211</v>
+      </c>
+      <c r="G28" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F8:G8"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F22:G22"/>
@@ -5365,6 +5350,15 @@
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F8:G8"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="F19:G19"/>
@@ -5388,784 +5382,806 @@
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
-        <v>215</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+        <v>212</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="A2" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="F3" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="28"/>
+      <c r="G3" s="34"/>
     </row>
     <row r="4" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
         <v>1</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D4" s="17">
         <v>6.3259999999999996</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="G4" s="22"/>
+        <v>215</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>216</v>
+      </c>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>2</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" s="20">
         <v>6.2450000000000001</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="G5" s="22"/>
+        <v>218</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="G5" s="26"/>
     </row>
     <row r="6" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>3</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D6" s="17">
         <v>6.2320000000000002</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="G6" s="22"/>
+        <v>221</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="G6" s="26"/>
     </row>
     <row r="7" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18">
         <v>4</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D7" s="20">
         <v>20.591000000000001</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="G7" s="22"/>
+        <v>224</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>5</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="17">
         <v>8.2539999999999996</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>230</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="G8" s="22"/>
+        <v>227</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D9" s="20">
         <v>8.2040000000000006</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="G9" s="22"/>
+        <v>230</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>7</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" s="17">
         <v>6.1529999999999996</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="G10" s="22"/>
+        <v>233</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="G10" s="26"/>
     </row>
     <row r="11" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18">
         <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D11" s="20">
         <v>6.1849999999999996</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="G11" s="22"/>
+        <v>236</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>9</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D12" s="17">
         <v>6.1289999999999996</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="G12" s="22"/>
+        <v>239</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>240</v>
+      </c>
+      <c r="G12" s="26"/>
     </row>
     <row r="13" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
         <v>10</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13" s="20">
         <v>6.1139999999999999</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>245</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="G13" s="22"/>
+        <v>242</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
         <v>11</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D14" s="17">
         <v>6.1660000000000004</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>249</v>
-      </c>
-      <c r="G14" s="22"/>
+        <v>245</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>246</v>
+      </c>
+      <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18">
         <v>12</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D15" s="20">
         <v>6.1449999999999996</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="G15" s="22"/>
+        <v>248</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="G15" s="26"/>
     </row>
     <row r="16" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
         <v>13</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D16" s="17">
         <v>6.1379999999999999</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>255</v>
-      </c>
-      <c r="G16" s="22"/>
+        <v>251</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>252</v>
+      </c>
+      <c r="G16" s="26"/>
     </row>
     <row r="17" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18">
         <v>14</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D17" s="20">
         <v>8.2899999999999991</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="G17" s="22"/>
+        <v>254</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="G17" s="26"/>
     </row>
     <row r="18" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
         <v>15</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D18" s="17">
         <v>15.009</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>261</v>
-      </c>
-      <c r="G18" s="22"/>
+        <v>257</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="G18" s="26"/>
     </row>
     <row r="19" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18">
         <v>16</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D19" s="20">
         <v>6.3540000000000001</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="G19" s="22"/>
+        <v>260</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="G19" s="26"/>
     </row>
     <row r="20" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
         <v>17</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D20" s="17">
         <v>9.2249999999999996</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="G20" s="22"/>
+        <v>263</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>264</v>
+      </c>
+      <c r="G20" s="26"/>
     </row>
     <row r="21" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18">
         <v>18</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D21" s="20">
         <v>9.2189999999999994</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="G21" s="22"/>
+        <v>266</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="G21" s="26"/>
     </row>
     <row r="22" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <v>19</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D22" s="17">
         <v>8.1709999999999994</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>272</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>273</v>
-      </c>
-      <c r="G22" s="22"/>
+        <v>269</v>
+      </c>
+      <c r="F22" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="G22" s="26"/>
     </row>
     <row r="23" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18">
         <v>20</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D23" s="20">
         <v>9.2479999999999993</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="G23" s="22"/>
+        <v>272</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="G23" s="26"/>
     </row>
     <row r="24" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
         <v>21</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D24" s="17">
         <v>6.1130000000000004</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>279</v>
-      </c>
-      <c r="G24" s="22"/>
+        <v>275</v>
+      </c>
+      <c r="F24" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="G24" s="26"/>
     </row>
     <row r="25" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
         <v>22</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D25" s="20">
         <v>6.1340000000000003</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="G25" s="22"/>
+        <v>278</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="G25" s="26"/>
     </row>
     <row r="26" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
         <v>23</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D26" s="17">
         <v>6.125</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="G26" s="22"/>
+        <v>281</v>
+      </c>
+      <c r="F26" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="G26" s="26"/>
     </row>
     <row r="27" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18">
         <v>24</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D27" s="20">
         <v>8.1159999999999997</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>288</v>
-      </c>
-      <c r="G27" s="22"/>
+        <v>284</v>
+      </c>
+      <c r="F27" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="G27" s="26"/>
     </row>
     <row r="28" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
         <v>25</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D28" s="17">
         <v>6.2619999999999996</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>290</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="G28" s="22"/>
+        <v>287</v>
+      </c>
+      <c r="F28" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="G28" s="26"/>
     </row>
     <row r="29" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="18">
         <v>26</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D29" s="20">
         <v>6.2290000000000001</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="F29" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="G29" s="22"/>
+        <v>290</v>
+      </c>
+      <c r="F29" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="G29" s="26"/>
     </row>
     <row r="30" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14">
         <v>27</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D30" s="17">
         <v>8.2520000000000007</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="F30" s="25" t="s">
-        <v>297</v>
-      </c>
-      <c r="G30" s="22"/>
+        <v>293</v>
+      </c>
+      <c r="F30" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="G30" s="26"/>
     </row>
     <row r="31" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="18">
         <v>28</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D31" s="20">
         <v>9.2140000000000004</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="F31" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="G31" s="22"/>
+        <v>296</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="G31" s="26"/>
     </row>
     <row r="32" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14">
         <v>29</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D32" s="17">
         <v>9.266</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="F32" s="25" t="s">
-        <v>303</v>
-      </c>
-      <c r="G32" s="22"/>
+        <v>299</v>
+      </c>
+      <c r="F32" s="31" t="s">
+        <v>300</v>
+      </c>
+      <c r="G32" s="26"/>
     </row>
     <row r="33" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="18">
         <v>30</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D33" s="20">
         <v>9.2379999999999995</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>305</v>
-      </c>
-      <c r="F33" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="G33" s="22"/>
+        <v>302</v>
+      </c>
+      <c r="F33" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="G33" s="26"/>
     </row>
     <row r="34" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14">
         <v>31</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D34" s="17">
         <v>6.2489999999999997</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>308</v>
-      </c>
-      <c r="F34" s="25" t="s">
-        <v>309</v>
-      </c>
-      <c r="G34" s="22"/>
+        <v>305</v>
+      </c>
+      <c r="F34" s="31" t="s">
+        <v>306</v>
+      </c>
+      <c r="G34" s="26"/>
     </row>
     <row r="35" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="18">
         <v>32</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D35" s="20">
         <v>10.228</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>311</v>
-      </c>
-      <c r="F35" s="26" t="s">
-        <v>312</v>
-      </c>
-      <c r="G35" s="22"/>
+        <v>308</v>
+      </c>
+      <c r="F35" s="30" t="s">
+        <v>309</v>
+      </c>
+      <c r="G35" s="26"/>
     </row>
     <row r="36" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="14">
         <v>33</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D36" s="17">
         <v>6.1950000000000003</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="F36" s="25" t="s">
-        <v>315</v>
-      </c>
-      <c r="G36" s="22"/>
+        <v>311</v>
+      </c>
+      <c r="F36" s="31" t="s">
+        <v>312</v>
+      </c>
+      <c r="G36" s="26"/>
     </row>
     <row r="37" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="18">
         <v>34</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D37" s="20">
         <v>6.1639999999999997</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>317</v>
-      </c>
-      <c r="F37" s="26" t="s">
-        <v>318</v>
-      </c>
-      <c r="G37" s="22"/>
+        <v>314</v>
+      </c>
+      <c r="F37" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="G37" s="26"/>
     </row>
     <row r="38" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="14">
         <v>35</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D38" s="17">
         <v>8.1720000000000006</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>320</v>
-      </c>
-      <c r="F38" s="25" t="s">
-        <v>321</v>
-      </c>
-      <c r="G38" s="22"/>
+        <v>317</v>
+      </c>
+      <c r="F38" s="31" t="s">
+        <v>318</v>
+      </c>
+      <c r="G38" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="F23:G23"/>
@@ -6182,28 +6198,6 @@
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F25:G25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6224,583 +6218,574 @@
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
-        <v>322</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+        <v>319</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="A2" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="F3" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="28"/>
+      <c r="G3" s="34"/>
     </row>
     <row r="4" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
         <v>1</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D4" s="17">
         <v>6.1669999999999998</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>324</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>325</v>
-      </c>
-      <c r="G4" s="22"/>
+        <v>321</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>322</v>
+      </c>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>2</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" s="20">
         <v>6.1609999999999996</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>328</v>
-      </c>
-      <c r="G5" s="22"/>
+        <v>324</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="G5" s="26"/>
     </row>
     <row r="6" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>3</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D6" s="17">
         <v>6.1589999999999998</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>330</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>331</v>
-      </c>
-      <c r="G6" s="22"/>
+        <v>327</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>328</v>
+      </c>
+      <c r="G6" s="26"/>
     </row>
     <row r="7" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18">
         <v>4</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D7" s="20">
         <v>8.3979999999999997</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="G7" s="22"/>
+        <v>330</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>5</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="17">
         <v>9.3770000000000007</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>337</v>
-      </c>
-      <c r="G8" s="22"/>
+        <v>333</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>334</v>
+      </c>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D9" s="20">
         <v>11.396000000000001</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>339</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>340</v>
-      </c>
-      <c r="G9" s="22"/>
+        <v>336</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>7</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" s="17">
         <v>11.648</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>343</v>
-      </c>
-      <c r="G10" s="22"/>
+        <v>339</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>340</v>
+      </c>
+      <c r="G10" s="26"/>
     </row>
     <row r="11" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18">
         <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D11" s="20">
         <v>16.943000000000001</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>346</v>
-      </c>
-      <c r="G11" s="22"/>
+        <v>342</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>343</v>
+      </c>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>9</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D12" s="17">
         <v>6.6050000000000004</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>349</v>
-      </c>
-      <c r="G12" s="22"/>
+        <v>345</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>346</v>
+      </c>
+      <c r="G12" s="26"/>
     </row>
     <row r="13" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
         <v>10</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13" s="20">
         <v>6.734</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>351</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>352</v>
-      </c>
-      <c r="G13" s="22"/>
+        <v>348</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>349</v>
+      </c>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
         <v>11</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D14" s="17">
         <v>6.41</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>354</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>355</v>
-      </c>
-      <c r="G14" s="22"/>
+        <v>351</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>352</v>
+      </c>
+      <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18">
         <v>12</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D15" s="20">
         <v>9.5540000000000003</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>357</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>358</v>
-      </c>
-      <c r="G15" s="22"/>
+        <v>354</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>355</v>
+      </c>
+      <c r="G15" s="26"/>
     </row>
     <row r="16" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
         <v>13</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D16" s="17">
         <v>9.4420000000000002</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>360</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>361</v>
-      </c>
-      <c r="G16" s="22"/>
+        <v>357</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>358</v>
+      </c>
+      <c r="G16" s="26"/>
     </row>
     <row r="17" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18">
         <v>14</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D17" s="20">
         <v>9.5519999999999996</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>363</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>364</v>
-      </c>
-      <c r="G17" s="22"/>
+        <v>360</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>361</v>
+      </c>
+      <c r="G17" s="26"/>
     </row>
     <row r="18" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
         <v>15</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D18" s="17">
         <v>8.3849999999999998</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>366</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>367</v>
-      </c>
-      <c r="G18" s="22"/>
+        <v>363</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>364</v>
+      </c>
+      <c r="G18" s="26"/>
     </row>
     <row r="19" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18">
         <v>16</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D19" s="20">
         <v>10.381</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>369</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>370</v>
-      </c>
-      <c r="G19" s="22"/>
+        <v>366</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>367</v>
+      </c>
+      <c r="G19" s="26"/>
     </row>
     <row r="20" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
         <v>17</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D20" s="17">
         <v>11.522</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>372</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="G20" s="22"/>
+        <v>369</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>370</v>
+      </c>
+      <c r="G20" s="26"/>
     </row>
     <row r="21" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18">
         <v>18</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D21" s="20">
         <v>8.4450000000000003</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>375</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>376</v>
-      </c>
-      <c r="G21" s="22"/>
+        <v>372</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>373</v>
+      </c>
+      <c r="G21" s="26"/>
     </row>
     <row r="22" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <v>19</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D22" s="17">
         <v>11.311999999999999</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>379</v>
-      </c>
-      <c r="G22" s="22"/>
+        <v>375</v>
+      </c>
+      <c r="F22" s="31" t="s">
+        <v>376</v>
+      </c>
+      <c r="G22" s="26"/>
     </row>
     <row r="23" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18">
         <v>20</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D23" s="20">
         <v>11.263999999999999</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>381</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>382</v>
-      </c>
-      <c r="G23" s="22"/>
+        <v>378</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>379</v>
+      </c>
+      <c r="G23" s="26"/>
     </row>
     <row r="24" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
         <v>21</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D24" s="17">
         <v>11.406000000000001</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>384</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>385</v>
-      </c>
-      <c r="G24" s="22"/>
+        <v>381</v>
+      </c>
+      <c r="F24" s="31" t="s">
+        <v>382</v>
+      </c>
+      <c r="G24" s="26"/>
     </row>
     <row r="25" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
         <v>22</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D25" s="20">
         <v>9.3209999999999997</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>387</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>388</v>
-      </c>
-      <c r="G25" s="22"/>
+        <v>384</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>385</v>
+      </c>
+      <c r="G25" s="26"/>
     </row>
     <row r="26" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
         <v>23</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D26" s="17">
         <v>6.2409999999999997</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>391</v>
-      </c>
-      <c r="G26" s="22"/>
+        <v>387</v>
+      </c>
+      <c r="F26" s="31" t="s">
+        <v>388</v>
+      </c>
+      <c r="G26" s="26"/>
     </row>
     <row r="27" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18">
         <v>24</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D27" s="20">
         <v>8.4090000000000007</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>393</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>394</v>
-      </c>
-      <c r="G27" s="22"/>
+        <v>390</v>
+      </c>
+      <c r="F27" s="30" t="s">
+        <v>391</v>
+      </c>
+      <c r="G27" s="26"/>
     </row>
     <row r="28" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
         <v>25</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D28" s="17">
         <v>8.2759999999999998</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>397</v>
-      </c>
-      <c r="G28" s="22"/>
+        <v>393</v>
+      </c>
+      <c r="F28" s="31" t="s">
+        <v>394</v>
+      </c>
+      <c r="G28" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F8:G8"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F22:G22"/>
@@ -6817,6 +6802,15 @@
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F8:G8"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="F19:G19"/>
@@ -6840,583 +6834,574 @@
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
-        <v>398</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+        <v>395</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="A2" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="F3" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="28"/>
+      <c r="G3" s="34"/>
     </row>
     <row r="4" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
         <v>1</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D4" s="17">
         <v>6.133</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>400</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>401</v>
-      </c>
-      <c r="G4" s="22"/>
+        <v>397</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>398</v>
+      </c>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>2</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" s="20">
         <v>6.1619999999999999</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>404</v>
-      </c>
-      <c r="G5" s="22"/>
+        <v>400</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>401</v>
+      </c>
+      <c r="G5" s="26"/>
     </row>
     <row r="6" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>3</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D6" s="17">
         <v>8.09</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>406</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>407</v>
-      </c>
-      <c r="G6" s="22"/>
+        <v>403</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>404</v>
+      </c>
+      <c r="G6" s="26"/>
     </row>
     <row r="7" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18">
         <v>4</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D7" s="20">
         <v>8.06</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>409</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>410</v>
-      </c>
-      <c r="G7" s="22"/>
+        <v>406</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>407</v>
+      </c>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>5</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="17">
         <v>6.1310000000000002</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>413</v>
-      </c>
-      <c r="G8" s="22"/>
+        <v>409</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>410</v>
+      </c>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D9" s="20">
         <v>8.0250000000000004</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>415</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>416</v>
-      </c>
-      <c r="G9" s="22"/>
+        <v>412</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>413</v>
+      </c>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>7</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" s="17">
         <v>8.0950000000000006</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>418</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>419</v>
-      </c>
-      <c r="G10" s="22"/>
+        <v>415</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>416</v>
+      </c>
+      <c r="G10" s="26"/>
     </row>
     <row r="11" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18">
         <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D11" s="20">
         <v>8.0679999999999996</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>421</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="G11" s="22"/>
+        <v>418</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>419</v>
+      </c>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>9</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D12" s="17">
         <v>10.125</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>424</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>425</v>
-      </c>
-      <c r="G12" s="22"/>
+        <v>421</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>422</v>
+      </c>
+      <c r="G12" s="26"/>
     </row>
     <row r="13" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
         <v>10</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13" s="20">
         <v>10.29</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>427</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>428</v>
-      </c>
-      <c r="G13" s="22"/>
+        <v>424</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>425</v>
+      </c>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
         <v>11</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D14" s="17">
         <v>10.079000000000001</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>431</v>
-      </c>
-      <c r="G14" s="22"/>
+        <v>427</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>428</v>
+      </c>
+      <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18">
         <v>12</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D15" s="20">
         <v>10.141999999999999</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>434</v>
-      </c>
-      <c r="G15" s="22"/>
+        <v>430</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>431</v>
+      </c>
+      <c r="G15" s="26"/>
     </row>
     <row r="16" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
         <v>13</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D16" s="17">
         <v>8.0190000000000001</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>437</v>
-      </c>
-      <c r="G16" s="22"/>
+        <v>433</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>434</v>
+      </c>
+      <c r="G16" s="26"/>
     </row>
     <row r="17" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18">
         <v>14</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D17" s="20">
         <v>17.190999999999999</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>440</v>
-      </c>
-      <c r="G17" s="22"/>
+        <v>436</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>437</v>
+      </c>
+      <c r="G17" s="26"/>
     </row>
     <row r="18" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
         <v>15</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D18" s="17">
         <v>12.347</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>443</v>
-      </c>
-      <c r="G18" s="22"/>
+        <v>439</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>440</v>
+      </c>
+      <c r="G18" s="26"/>
     </row>
     <row r="19" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18">
         <v>16</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D19" s="20">
         <v>8.1379999999999999</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>446</v>
-      </c>
-      <c r="G19" s="22"/>
+        <v>442</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>443</v>
+      </c>
+      <c r="G19" s="26"/>
     </row>
     <row r="20" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
         <v>17</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D20" s="17">
         <v>8.1359999999999992</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>448</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>449</v>
-      </c>
-      <c r="G20" s="22"/>
+        <v>445</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>446</v>
+      </c>
+      <c r="G20" s="26"/>
     </row>
     <row r="21" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18">
         <v>18</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D21" s="20">
         <v>8.1519999999999992</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>452</v>
-      </c>
-      <c r="G21" s="22"/>
+        <v>448</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>449</v>
+      </c>
+      <c r="G21" s="26"/>
     </row>
     <row r="22" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <v>19</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D22" s="17">
         <v>9.1359999999999992</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>454</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>455</v>
-      </c>
-      <c r="G22" s="22"/>
+        <v>451</v>
+      </c>
+      <c r="F22" s="31" t="s">
+        <v>452</v>
+      </c>
+      <c r="G22" s="26"/>
     </row>
     <row r="23" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18">
         <v>20</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D23" s="20">
         <v>10.148999999999999</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>458</v>
-      </c>
-      <c r="G23" s="22"/>
+        <v>454</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>455</v>
+      </c>
+      <c r="G23" s="26"/>
     </row>
     <row r="24" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
         <v>21</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D24" s="17">
         <v>6.0949999999999998</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>460</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>461</v>
-      </c>
-      <c r="G24" s="22"/>
+        <v>457</v>
+      </c>
+      <c r="F24" s="31" t="s">
+        <v>458</v>
+      </c>
+      <c r="G24" s="26"/>
     </row>
     <row r="25" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
         <v>22</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D25" s="20">
         <v>8.0950000000000006</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>464</v>
-      </c>
-      <c r="G25" s="22"/>
+        <v>460</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>461</v>
+      </c>
+      <c r="G25" s="26"/>
     </row>
     <row r="26" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
         <v>23</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D26" s="17">
         <v>8.1300000000000008</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>466</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>467</v>
-      </c>
-      <c r="G26" s="22"/>
+        <v>463</v>
+      </c>
+      <c r="F26" s="31" t="s">
+        <v>464</v>
+      </c>
+      <c r="G26" s="26"/>
     </row>
     <row r="27" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18">
         <v>24</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D27" s="20">
         <v>8.1059999999999999</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>469</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>470</v>
-      </c>
-      <c r="G27" s="22"/>
+        <v>466</v>
+      </c>
+      <c r="F27" s="30" t="s">
+        <v>467</v>
+      </c>
+      <c r="G27" s="26"/>
     </row>
     <row r="28" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
         <v>25</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D28" s="17">
         <v>10.215</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>472</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>473</v>
-      </c>
-      <c r="G28" s="22"/>
+        <v>469</v>
+      </c>
+      <c r="F28" s="31" t="s">
+        <v>470</v>
+      </c>
+      <c r="G28" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F8:G8"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F22:G22"/>
@@ -7433,6 +7418,15 @@
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F8:G8"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="F19:G19"/>
@@ -7456,364 +7450,370 @@
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
-        <v>474</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+        <v>471</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
-        <v>475</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="A2" s="32" t="s">
+        <v>472</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="F3" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="28"/>
+      <c r="G3" s="34"/>
     </row>
     <row r="4" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
         <v>1</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D4" s="17">
         <v>7.335</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>477</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>478</v>
-      </c>
-      <c r="G4" s="22"/>
+        <v>474</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>475</v>
+      </c>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>2</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" s="20">
         <v>7.4009999999999998</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>481</v>
-      </c>
-      <c r="G5" s="22"/>
+        <v>477</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>478</v>
+      </c>
+      <c r="G5" s="26"/>
     </row>
     <row r="6" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>3</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D6" s="17">
         <v>7.3490000000000002</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>483</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>484</v>
-      </c>
-      <c r="G6" s="22"/>
+        <v>480</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>481</v>
+      </c>
+      <c r="G6" s="26"/>
     </row>
     <row r="7" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18">
         <v>4</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D7" s="20">
         <v>7.3310000000000004</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>487</v>
-      </c>
-      <c r="G7" s="22"/>
+        <v>483</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>484</v>
+      </c>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>5</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="17">
         <v>7.3410000000000002</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>490</v>
-      </c>
-      <c r="G8" s="22"/>
+        <v>486</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>487</v>
+      </c>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D9" s="20">
         <v>7.3209999999999997</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>493</v>
-      </c>
-      <c r="G9" s="22"/>
+        <v>489</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>490</v>
+      </c>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>7</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" s="17">
         <v>7.4029999999999996</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>495</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>496</v>
-      </c>
-      <c r="G10" s="22"/>
+        <v>492</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>493</v>
+      </c>
+      <c r="G10" s="26"/>
     </row>
     <row r="11" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18">
         <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>497</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>48</v>
+        <v>494</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>45</v>
       </c>
       <c r="D11" s="20">
         <v>7.1429999999999998</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>499</v>
-      </c>
-      <c r="G11" s="22"/>
+        <v>495</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>496</v>
+      </c>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>9</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D12" s="17">
         <v>7.3410000000000002</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>501</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>502</v>
-      </c>
-      <c r="G12" s="22"/>
+        <v>498</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>499</v>
+      </c>
+      <c r="G12" s="26"/>
     </row>
     <row r="13" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
         <v>10</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13" s="20">
         <v>19.564</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>504</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>505</v>
-      </c>
-      <c r="G13" s="22"/>
+        <v>501</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>502</v>
+      </c>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
         <v>11</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D14" s="17">
         <v>9.2780000000000005</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>507</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>508</v>
-      </c>
-      <c r="G14" s="22"/>
+        <v>504</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>505</v>
+      </c>
+      <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18">
         <v>12</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D15" s="20">
         <v>7.2270000000000003</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>510</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>511</v>
-      </c>
-      <c r="G15" s="22"/>
+        <v>507</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>508</v>
+      </c>
+      <c r="G15" s="26"/>
     </row>
     <row r="16" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
         <v>13</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D16" s="17">
         <v>9.2769999999999992</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>514</v>
-      </c>
-      <c r="G16" s="22"/>
+        <v>510</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>511</v>
+      </c>
+      <c r="G16" s="26"/>
     </row>
     <row r="17" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18">
         <v>14</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D17" s="20">
         <v>7.37</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>517</v>
-      </c>
-      <c r="G17" s="22"/>
+        <v>513</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>514</v>
+      </c>
+      <c r="G17" s="26"/>
     </row>
     <row r="18" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
         <v>15</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D18" s="17">
         <v>9.2870000000000008</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>519</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>520</v>
-      </c>
-      <c r="G18" s="22"/>
+        <v>516</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>517</v>
+      </c>
+      <c r="G18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="F16:G16"/>
@@ -7826,12 +7826,6 @@
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7853,583 +7847,574 @@
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
-        <v>521</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+        <v>518</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="A2" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="F3" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="28"/>
+      <c r="G3" s="34"/>
     </row>
     <row r="4" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
         <v>1</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D4" s="17">
         <v>6.1630000000000003</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>523</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>524</v>
-      </c>
-      <c r="G4" s="22"/>
+        <v>520</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>521</v>
+      </c>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>2</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" s="20">
         <v>6.1459999999999999</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>526</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>527</v>
-      </c>
-      <c r="G5" s="22"/>
+        <v>523</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>524</v>
+      </c>
+      <c r="G5" s="26"/>
     </row>
     <row r="6" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>3</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D6" s="17">
         <v>6.18</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>529</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>530</v>
-      </c>
-      <c r="G6" s="22"/>
+        <v>526</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>527</v>
+      </c>
+      <c r="G6" s="26"/>
     </row>
     <row r="7" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18">
         <v>4</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D7" s="20">
         <v>6.1609999999999996</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>532</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>533</v>
-      </c>
-      <c r="G7" s="22"/>
+        <v>529</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>530</v>
+      </c>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>5</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="17">
         <v>6.1539999999999999</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>535</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>536</v>
-      </c>
-      <c r="G8" s="22"/>
+        <v>532</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>533</v>
+      </c>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D9" s="20">
         <v>6.1479999999999997</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>538</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>539</v>
-      </c>
-      <c r="G9" s="22"/>
+        <v>535</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>536</v>
+      </c>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>7</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" s="17">
         <v>6.1580000000000004</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>541</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>542</v>
-      </c>
-      <c r="G10" s="22"/>
+        <v>538</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>539</v>
+      </c>
+      <c r="G10" s="26"/>
     </row>
     <row r="11" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18">
         <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D11" s="20">
         <v>8.2899999999999991</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>544</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>545</v>
-      </c>
-      <c r="G11" s="22"/>
+        <v>541</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>542</v>
+      </c>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>9</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D12" s="17">
         <v>6.1319999999999997</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>547</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>548</v>
-      </c>
-      <c r="G12" s="22"/>
+        <v>544</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>545</v>
+      </c>
+      <c r="G12" s="26"/>
     </row>
     <row r="13" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
         <v>10</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13" s="20">
         <v>8.2070000000000007</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>550</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>551</v>
-      </c>
-      <c r="G13" s="22"/>
+        <v>547</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
         <v>11</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D14" s="17">
         <v>9.2140000000000004</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>553</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>554</v>
-      </c>
-      <c r="G14" s="22"/>
+        <v>550</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>551</v>
+      </c>
+      <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18">
         <v>12</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D15" s="20">
         <v>11.257</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>556</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>557</v>
-      </c>
-      <c r="G15" s="22"/>
+        <v>553</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>554</v>
+      </c>
+      <c r="G15" s="26"/>
     </row>
     <row r="16" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
         <v>13</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D16" s="17">
         <v>5.1100000000000003</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>559</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>560</v>
-      </c>
-      <c r="G16" s="22"/>
+        <v>556</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>557</v>
+      </c>
+      <c r="G16" s="26"/>
     </row>
     <row r="17" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18">
         <v>14</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D17" s="20">
         <v>6.1639999999999997</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>562</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>563</v>
-      </c>
-      <c r="G17" s="22"/>
+        <v>559</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>560</v>
+      </c>
+      <c r="G17" s="26"/>
     </row>
     <row r="18" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
         <v>15</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D18" s="17">
         <v>6.2039999999999997</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>565</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>566</v>
-      </c>
-      <c r="G18" s="22"/>
+        <v>562</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>563</v>
+      </c>
+      <c r="G18" s="26"/>
     </row>
     <row r="19" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18">
         <v>16</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D19" s="20">
         <v>8.1590000000000007</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>568</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>569</v>
-      </c>
-      <c r="G19" s="22"/>
+        <v>565</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>566</v>
+      </c>
+      <c r="G19" s="26"/>
     </row>
     <row r="20" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
         <v>17</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D20" s="17">
         <v>8.1780000000000008</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>571</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>572</v>
-      </c>
-      <c r="G20" s="22"/>
+        <v>568</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>569</v>
+      </c>
+      <c r="G20" s="26"/>
     </row>
     <row r="21" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18">
         <v>18</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D21" s="20">
         <v>10.208</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>574</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>575</v>
-      </c>
-      <c r="G21" s="22"/>
+        <v>571</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>572</v>
+      </c>
+      <c r="G21" s="26"/>
     </row>
     <row r="22" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <v>19</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D22" s="17">
         <v>8.14</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>577</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>578</v>
-      </c>
-      <c r="G22" s="22"/>
+        <v>574</v>
+      </c>
+      <c r="F22" s="31" t="s">
+        <v>575</v>
+      </c>
+      <c r="G22" s="26"/>
     </row>
     <row r="23" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18">
         <v>20</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D23" s="20">
         <v>8.2289999999999992</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>580</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>581</v>
-      </c>
-      <c r="G23" s="22"/>
+        <v>577</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>578</v>
+      </c>
+      <c r="G23" s="26"/>
     </row>
     <row r="24" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
         <v>21</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D24" s="17">
         <v>8.2620000000000005</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>583</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>584</v>
-      </c>
-      <c r="G24" s="22"/>
+        <v>580</v>
+      </c>
+      <c r="F24" s="31" t="s">
+        <v>581</v>
+      </c>
+      <c r="G24" s="26"/>
     </row>
     <row r="25" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18">
         <v>22</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D25" s="20">
         <v>8.1639999999999997</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>586</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>587</v>
-      </c>
-      <c r="G25" s="22"/>
+        <v>583</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>584</v>
+      </c>
+      <c r="G25" s="26"/>
     </row>
     <row r="26" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
         <v>23</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D26" s="17">
         <v>6.3310000000000004</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>589</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>590</v>
-      </c>
-      <c r="G26" s="22"/>
+        <v>586</v>
+      </c>
+      <c r="F26" s="31" t="s">
+        <v>587</v>
+      </c>
+      <c r="G26" s="26"/>
     </row>
     <row r="27" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18">
         <v>24</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D27" s="20">
         <v>8.2810000000000006</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>592</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>593</v>
-      </c>
-      <c r="G27" s="22"/>
+        <v>589</v>
+      </c>
+      <c r="F27" s="30" t="s">
+        <v>590</v>
+      </c>
+      <c r="G27" s="26"/>
     </row>
     <row r="28" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
         <v>25</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D28" s="17">
         <v>8.2710000000000008</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>595</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>596</v>
-      </c>
-      <c r="G28" s="22"/>
+        <v>592</v>
+      </c>
+      <c r="F28" s="31" t="s">
+        <v>593</v>
+      </c>
+      <c r="G28" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F8:G8"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F22:G22"/>
@@ -8446,6 +8431,15 @@
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F8:G8"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="F19:G19"/>
@@ -8469,364 +8463,370 @@
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
-        <v>597</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+        <v>594</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
-        <v>598</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="A2" s="32" t="s">
+        <v>595</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="F3" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="28"/>
+      <c r="G3" s="34"/>
     </row>
     <row r="4" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
         <v>1</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D4" s="17">
         <v>6.3479999999999999</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>600</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>601</v>
-      </c>
-      <c r="G4" s="22"/>
+        <v>597</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>598</v>
+      </c>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>2</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" s="20">
         <v>6.29</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>603</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>604</v>
-      </c>
-      <c r="G5" s="22"/>
+        <v>600</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>601</v>
+      </c>
+      <c r="G5" s="26"/>
     </row>
     <row r="6" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>3</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D6" s="17">
         <v>6.3010000000000002</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>606</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>607</v>
-      </c>
-      <c r="G6" s="22"/>
+        <v>603</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>604</v>
+      </c>
+      <c r="G6" s="26"/>
     </row>
     <row r="7" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18">
         <v>4</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D7" s="20">
         <v>6.3070000000000004</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>609</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>610</v>
-      </c>
-      <c r="G7" s="22"/>
+        <v>606</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>607</v>
+      </c>
+      <c r="G7" s="26"/>
     </row>
     <row r="8" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>5</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="17">
         <v>6.2469999999999999</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>612</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>613</v>
-      </c>
-      <c r="G8" s="22"/>
+        <v>609</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>610</v>
+      </c>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D9" s="20">
         <v>6.31</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>615</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>616</v>
-      </c>
-      <c r="G9" s="22"/>
+        <v>612</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>613</v>
+      </c>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>7</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" s="17">
         <v>6.2869999999999999</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>618</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>619</v>
-      </c>
-      <c r="G10" s="22"/>
+        <v>615</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>616</v>
+      </c>
+      <c r="G10" s="26"/>
     </row>
     <row r="11" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18">
         <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D11" s="20">
         <v>6.2350000000000003</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>621</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>622</v>
-      </c>
-      <c r="G11" s="22"/>
+        <v>618</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>619</v>
+      </c>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>9</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D12" s="17">
         <v>6.327</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>624</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>625</v>
-      </c>
-      <c r="G12" s="22"/>
+        <v>621</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>622</v>
+      </c>
+      <c r="G12" s="26"/>
     </row>
     <row r="13" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
         <v>10</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13" s="20">
         <v>17.353000000000002</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>627</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>628</v>
-      </c>
-      <c r="G13" s="22"/>
+        <v>624</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>625</v>
+      </c>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
         <v>11</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D14" s="17">
         <v>8.3249999999999993</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>630</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>631</v>
-      </c>
-      <c r="G14" s="22"/>
+        <v>627</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>628</v>
+      </c>
+      <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18">
         <v>12</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D15" s="20">
         <v>8.2119999999999997</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>633</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>634</v>
-      </c>
-      <c r="G15" s="22"/>
+        <v>630</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>631</v>
+      </c>
+      <c r="G15" s="26"/>
     </row>
     <row r="16" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
         <v>13</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D16" s="17">
         <v>7.3860000000000001</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>636</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>637</v>
-      </c>
-      <c r="G16" s="22"/>
+        <v>633</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>634</v>
+      </c>
+      <c r="G16" s="26"/>
     </row>
     <row r="17" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18">
         <v>14</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D17" s="20">
         <v>8.2460000000000004</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>639</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>640</v>
-      </c>
-      <c r="G17" s="22"/>
+        <v>636</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>637</v>
+      </c>
+      <c r="G17" s="26"/>
     </row>
     <row r="18" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
         <v>15</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D18" s="17">
         <v>8.2840000000000007</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>642</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>643</v>
-      </c>
-      <c r="G18" s="22"/>
+        <v>639</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>640</v>
+      </c>
+      <c r="G18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="F16:G16"/>
@@ -8839,12 +8839,6 @@
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
